--- a/data/editorial_es.xlsx
+++ b/data/editorial_es.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t xml:space="preserve">what</t>
   </si>
@@ -37,25 +37,22 @@
     <t xml:space="preserve">why</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Editor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\href{https://royalsocietypublishing.org/journal/rspb}{Proceedings of the Royal Society B}</t>
+    <t xml:space="preserve">Associate Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://evohuman.org}{Evolutionary Dynamics of Human Behavior (EDHB)}</t>
   </si>
   <si>
     <t xml:space="preserve">Equipo editorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Verificar el cumplimiento de los estándares de disponibilidad de datos y código antes de la aceptación de los artículos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprobar que los conjuntos de datos, códigos y materiales de investigación estén completos, sean accesibles y coherentes con los resultados reportados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientar a los autores que no cumplan con las políticas de datos abiertos, indicando los ajustes necesarios</t>
+    <t xml:space="preserve">Seleccionar revisores adecuados y gestionar el proceso de revisión de pares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuir al consejo editorial, centrándose en la representación y la diversidad del Sur Global</t>
   </si>
   <si>
     <r>
@@ -63,10 +60,10 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">\href{https://royalsocietypublishing.org/rspb/pages/Editorial_Board}{</t>
+      <t xml:space="preserve">\href{https://evohuman.org/edhb/editorial-board}{</t>
     </r>
     <r>
       <rPr>
@@ -82,11 +79,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://royalsocietypublishing.org/journal/rspb}{Proceedings of the Royal Society B}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar el cumplimiento de los estándares de disponibilidad de datos y código antes de la aceptación de los artículos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprobar que los conjuntos de datos, códigos y materiales de investigación estén completos, sean accesibles y coherentes con los resultados reportados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientar a los autores que no cumplan con las políticas de datos abiertos, indicando los ajustes necesarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://royalsocietypublishing.org/rspb/pages/Editorial_Board}{Comité editorial}</t>
   </si>
   <si>
     <t xml:space="preserve">Recommender (equivalente a Editor Asociado)</t>
@@ -233,7 +251,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +280,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -319,7 +343,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -328,11 +352,15 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,7 +368,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -533,8 +561,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.29"/>
@@ -544,7 +572,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.43"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -578,16 +606,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -596,224 +624,260 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="1" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="1" t="s">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="1" t="s">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="1" t="s">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="1" t="s">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="5"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="5"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="5"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="6"/>
       <c r="E28" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="6"/>
       <c r="E29" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="1" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="6"/>
+      <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="1" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="6"/>
+      <c r="E31" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="1" t="s">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="1" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E16" r:id="rId1" display="\href{https://nyaspubs.onlinelibrary.wiley.com/journal/17496632}{Annals of the New York Academy of Sciences}"/>
+    <hyperlink ref="E4" r:id="rId1" display="https://evohuman.org/edhb/editorial-board"/>
+    <hyperlink ref="E19" r:id="rId2" display="\href{https://nyaspubs.onlinelibrary.wiley.com/journal/17496632}{Annals of the New York Academy of Sciences}"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
